--- a/GridFlexPy/data/spreadsheets/sheet_IEEE13Node.xlsx
+++ b/GridFlexPy/data/spreadsheets/sheet_IEEE13Node.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao9\GitHub\GridFlexPy\data\spreadsheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao9\GitHub\IA367-Aprendizado-Reforco\GridFlexPy\data\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09ECCB1E-BD5A-49D5-B6A1-444F37957736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA613CB-714B-4548-A68E-7F26C0E639AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -787,7 +787,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1037,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>41097.291666666664</v>
+        <v>41698</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>20</v>

--- a/GridFlexPy/data/spreadsheets/sheet_IEEE13Node.xlsx
+++ b/GridFlexPy/data/spreadsheets/sheet_IEEE13Node.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao9\GitHub\IA367-Aprendizado-Reforco\GridFlexPy\data\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA613CB-714B-4548-A68E-7F26C0E639AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D10E3BA-7FF4-4A7A-A6FE-994FECD76DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1026,7 +1026,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3">
-        <v>41096.5</v>
+        <v>41097.25</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>20</v>
